--- a/artfynd/A 40296-2025 artfynd.xlsx
+++ b/artfynd/A 40296-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>136337803</v>
       </c>
       <c r="B3" t="n">
-        <v>99327</v>
+        <v>99330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40296-2025 artfynd.xlsx
+++ b/artfynd/A 40296-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>136337803</v>
       </c>
       <c r="B3" t="n">
-        <v>99330</v>
+        <v>99331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40296-2025 artfynd.xlsx
+++ b/artfynd/A 40296-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>136337803</v>
       </c>
       <c r="B3" t="n">
-        <v>99331</v>
+        <v>99336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40296-2025 artfynd.xlsx
+++ b/artfynd/A 40296-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>136337803</v>
       </c>
       <c r="B3" t="n">
-        <v>99336</v>
+        <v>99338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40296-2025 artfynd.xlsx
+++ b/artfynd/A 40296-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>136337803</v>
       </c>
       <c r="B3" t="n">
-        <v>99338</v>
+        <v>99344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40296-2025 artfynd.xlsx
+++ b/artfynd/A 40296-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>136337803</v>
       </c>
       <c r="B3" t="n">
-        <v>99344</v>
+        <v>99346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
